--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>75.5146672657613</v>
+        <v>12.27113343068621</v>
       </c>
       <c r="D2" t="n">
-        <v>57.43522700612248</v>
+        <v>9.333224388494903</v>
       </c>
       <c r="E2" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F2" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68.70821429569942</v>
+        <v>11.16508482305116</v>
       </c>
       <c r="D3" t="n">
-        <v>51.70403548837056</v>
+        <v>8.401905766860216</v>
       </c>
       <c r="E3" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F3" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>78.44082202344265</v>
+        <v>12.74663357880943</v>
       </c>
       <c r="D4" t="n">
-        <v>50.92982488507267</v>
+        <v>8.276096543824309</v>
       </c>
       <c r="E4" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F4" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>85.47216596251435</v>
+        <v>13.88922696890858</v>
       </c>
       <c r="D5" t="n">
-        <v>53.0873365301394</v>
+        <v>8.626692186147652</v>
       </c>
       <c r="E5" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F5" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.84995355735218</v>
+        <v>4.20061745306973</v>
       </c>
       <c r="D6" t="n">
-        <v>26.26065267182607</v>
+        <v>4.267356059171737</v>
       </c>
       <c r="E6" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F6" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.53292673659231</v>
+        <v>2.52410059469625</v>
       </c>
       <c r="D7" t="n">
-        <v>15.53333649253019</v>
+        <v>2.524167180036156</v>
       </c>
       <c r="E7" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F7" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.70007991816194</v>
+        <v>4.826262986701315</v>
       </c>
       <c r="D8" t="n">
-        <v>30.01339740240887</v>
+        <v>4.877177077891441</v>
       </c>
       <c r="E8" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F8" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.81232376241208</v>
+        <v>6.469502611391964</v>
       </c>
       <c r="D9" t="n">
-        <v>48.00796481162325</v>
+        <v>7.801294281888779</v>
       </c>
       <c r="E9" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F9" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.69542972800816</v>
+        <v>5.475507330801327</v>
       </c>
       <c r="D10" t="n">
-        <v>44.3942634244561</v>
+        <v>7.214067806474116</v>
       </c>
       <c r="E10" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F10" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.60973345812958</v>
+        <v>6.761581686946057</v>
       </c>
       <c r="D11" t="n">
-        <v>42.94431909157525</v>
+        <v>6.978451852380978</v>
       </c>
       <c r="E11" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F11" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.97764754762551</v>
+        <v>3.571367726489146</v>
       </c>
       <c r="D12" t="n">
-        <v>12.41010361045193</v>
+        <v>2.016641836698439</v>
       </c>
       <c r="E12" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F12" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.56281201479724</v>
+        <v>3.666456952404552</v>
       </c>
       <c r="D13" t="n">
-        <v>39.80276372313863</v>
+        <v>6.467949105010026</v>
       </c>
       <c r="E13" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F13" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>20.99510602229428</v>
+        <v>3.41170472862282</v>
       </c>
       <c r="D14" t="n">
-        <v>15.35083884413926</v>
+        <v>2.494511312172629</v>
       </c>
       <c r="E14" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F14" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>24.78001872751618</v>
+        <v>4.02675304322138</v>
       </c>
       <c r="D15" t="n">
-        <v>25.51621033028567</v>
+        <v>4.146384178671422</v>
       </c>
       <c r="E15" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F15" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>40.33948323183377</v>
+        <v>6.555166025172989</v>
       </c>
       <c r="D16" t="n">
-        <v>31.77800647463163</v>
+        <v>5.16392605212764</v>
       </c>
       <c r="E16" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F16" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>39.7406160603941</v>
+        <v>6.457850109814041</v>
       </c>
       <c r="D17" t="n">
-        <v>7.761951446460134</v>
+        <v>1.261317110049772</v>
       </c>
       <c r="E17" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F17" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>37.23308323993381</v>
+        <v>6.050376026489245</v>
       </c>
       <c r="D18" t="n">
-        <v>8.593706498549968</v>
+        <v>1.39647730601437</v>
       </c>
       <c r="E18" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F18" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>48.01302973250966</v>
+        <v>7.802117331532821</v>
       </c>
       <c r="D19" t="n">
-        <v>34.63724518961142</v>
+        <v>5.628552343311856</v>
       </c>
       <c r="E19" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F19" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>27.61461419113706</v>
+        <v>4.487374806059772</v>
       </c>
       <c r="D20" t="n">
-        <v>2.135236728106789</v>
+        <v>0.3469759683173532</v>
       </c>
       <c r="E20" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F20" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>61.86401482060428</v>
+        <v>10.0529024083482</v>
       </c>
       <c r="D21" t="n">
-        <v>22.31248060981216</v>
+        <v>3.625778099094477</v>
       </c>
       <c r="E21" t="n">
-        <v>20.5250146009731</v>
+        <v>3.33531487265813</v>
       </c>
       <c r="F21" t="n">
-        <v>16.65694585442638</v>
+        <v>2.706753701344287</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
